--- a/preview/OR.PA/OR.PA_financials.xlsx
+++ b/preview/OR.PA/OR.PA_financials.xlsx
@@ -8055,10 +8055,18 @@
         </is>
       </c>
       <c r="D29" s="266" t="n"/>
-      <c r="E29" s="266" t="n"/>
-      <c r="F29" s="266" t="n"/>
-      <c r="G29" s="266" t="n"/>
-      <c r="H29" s="266" t="n"/>
+      <c r="E29" s="266" t="n">
+        <v>-502.3</v>
+      </c>
+      <c r="F29" s="266" t="n">
+        <v>-503.3</v>
+      </c>
+      <c r="G29" s="266" t="n">
+        <v>-497.5</v>
+      </c>
+      <c r="H29" s="266" t="n">
+        <v>-501.5</v>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="3" t="n"/>
@@ -9095,10 +9103,18 @@
         </is>
       </c>
       <c r="D79" s="266" t="n"/>
-      <c r="E79" s="266" t="n"/>
-      <c r="F79" s="266" t="n"/>
-      <c r="G79" s="266" t="n"/>
-      <c r="H79" s="266" t="n"/>
+      <c r="E79" s="266" t="n">
+        <v>-142.8</v>
+      </c>
+      <c r="F79" s="266" t="n">
+        <v>-170.7</v>
+      </c>
+      <c r="G79" s="266" t="n">
+        <v>-1927</v>
+      </c>
+      <c r="H79" s="266" t="n">
+        <v>2509</v>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
       <c r="A80" s="3" t="n"/>

--- a/preview/OR.PA/OR.PA_financials.xlsx
+++ b/preview/OR.PA/OR.PA_financials.xlsx
@@ -20439,7 +20439,7 @@
       </c>
       <c r="J9" s="479" t="n"/>
       <c r="K9" s="477" t="n">
-        <v>5.07</v>
+        <v>5.05</v>
       </c>
       <c r="L9" s="478">
         <f>IFERROR(D9/K9,"–")</f>

--- a/preview/OR.PA/OR.PA_financials.xlsx
+++ b/preview/OR.PA/OR.PA_financials.xlsx
@@ -8702,10 +8702,18 @@
         </is>
       </c>
       <c r="D59" s="276" t="n"/>
-      <c r="E59" s="276" t="n"/>
-      <c r="F59" s="276" t="n"/>
-      <c r="G59" s="276" t="n"/>
-      <c r="H59" s="276" t="n"/>
+      <c r="E59" s="276" t="n">
+        <v>5706.6</v>
+      </c>
+      <c r="F59" s="276" t="n">
+        <v>6184</v>
+      </c>
+      <c r="G59" s="276" t="n">
+        <v>6408.7</v>
+      </c>
+      <c r="H59" s="276" t="n">
+        <v>6127.2</v>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="3" t="n"/>
